--- a/testdata/TaskCategory.xlsx
+++ b/testdata/TaskCategory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\stp-automation-test\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFE45E9-18C4-43F9-AFB9-3649BA515641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A15908-BC20-426B-ABD8-2A9765332AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C7681F3F-D0BE-43DE-AC81-0EAE175E5E0E}"/>
   </bookViews>
@@ -40,12 +40,6 @@
     <t xml:space="preserve"> expectedResult</t>
   </si>
   <si>
-    <t>Task 1</t>
-  </si>
-  <si>
-    <t>Task 2</t>
-  </si>
-  <si>
     <t>TaskCategoryName</t>
   </si>
   <si>
@@ -53,6 +47,12 @@
   </si>
   <si>
     <t>This task category was successfully changed</t>
+  </si>
+  <si>
+    <t>Selling</t>
+  </si>
+  <si>
+    <t>Buying</t>
   </si>
 </sst>
 </file>
@@ -434,7 +434,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -442,18 +442,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -474,7 +474,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -482,18 +482,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
